--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261015.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261015.xlsx
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>23,694,000</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,733,000</t>
+          <t>20,037,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>20,037,000</t>
+          <t>6,733,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
